--- a/laiko-ataskaita/PSP-ED.xlsx
+++ b/laiko-ataskaita/PSP-ED.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1827BB7B-75FC-45C0-B406-675EC1A92B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D9E58C-CF06-4654-B95D-BE431F3C417B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Data</t>
   </si>
@@ -55,6 +55,12 @@
   </si>
   <si>
     <t>diagramų kūrimas</t>
+  </si>
+  <si>
+    <t>kodavimas</t>
+  </si>
+  <si>
+    <t>testavimas</t>
   </si>
 </sst>
 </file>
@@ -486,34 +492,67 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="A3" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5493055555555556</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.61597222222222225</v>
+      </c>
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D5" si="0">C3-B3</f>
+        <v>6.6666666666666652E-2</v>
+      </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="A4" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.61597222222222225</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>2.2916666666666585E-2</v>
+      </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="A5" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.8194444444444531E-2</v>
+      </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="5"/>
+      <c r="A6" s="3"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -522,7 +561,7 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="5"/>
+      <c r="A7" s="3"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>

--- a/laiko-ataskaita/PSP-ED.xlsx
+++ b/laiko-ataskaita/PSP-ED.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D9E58C-CF06-4654-B95D-BE431F3C417B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13EA1119-7171-4C47-B2CA-3CF320AFE704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Data</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>testavimas</t>
+  </si>
+  <si>
+    <t>komandos kodo tikrinimas ir klaidų taisymas</t>
+  </si>
+  <si>
+    <t>kodavimas, diagramų kūrimas</t>
   </si>
 </sst>
 </file>
@@ -444,7 +450,7 @@
     <col min="3" max="3" width="13.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="41.28515625" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -502,7 +508,7 @@
         <v>0.61597222222222225</v>
       </c>
       <c r="D3" s="4">
-        <f t="shared" ref="D3:D5" si="0">C3-B3</f>
+        <f t="shared" ref="D3:D7" si="0">C3-B3</f>
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="E3" s="5"/>
@@ -552,21 +558,43 @@
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="A6" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>9.4444444444444442E-2</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>4.2361111111111106E-2</v>
+      </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="3"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="A7" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B7" s="4">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>2.7083333333333331E-2</v>
+      </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7">
